--- a/server/upload/excel_template/ORDER_LIST.xlsx
+++ b/server/upload/excel_template/ORDER_LIST.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t xml:space="preserve">Order List</t>
   </si>
@@ -49,9 +49,6 @@
   </si>
   <si>
     <t xml:space="preserve">Ord Qty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO Qty</t>
   </si>
   <si>
     <t xml:space="preserve">Add</t>
@@ -580,25 +577,25 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Y7"/>
-  <sheetFormatPr defaultColWidth="8.87890625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:X7"/>
+  <sheetFormatPr defaultColWidth="8.87890625" defaultRowHeight="12.65" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="12.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="12.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="12.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="7" style="3" width="8.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="4" width="8.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="3" width="8.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="4" width="8.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="15" style="5" width="8.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="6" width="9.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="6" width="5.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="6" width="12.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="6" width="9.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="6" width="10.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="24" style="6" width="12.66"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="27" style="6" width="8.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="3" width="8.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="4" width="8.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="3" width="8.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="4" width="8.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="14" style="5" width="8.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="6" width="9.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="6" width="5.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="6" width="12.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="6" width="9.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="6" width="10.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="23" style="6" width="12.66"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="25" style="6" width="8.88"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -608,21 +605,21 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="10"/>
       <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
+      <c r="N2" s="11"/>
       <c r="O2" s="11"/>
       <c r="P2" s="11"/>
       <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
+      <c r="R2" s="12"/>
       <c r="S2" s="12"/>
       <c r="T2" s="12"/>
       <c r="U2" s="12"/>
-      <c r="V2" s="12"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
         <v>1</v>
       </c>
@@ -650,19 +647,19 @@
       <c r="I3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="K3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="14" t="s">
+      <c r="L3" s="15" t="s">
         <v>12</v>
       </c>
       <c r="M3" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="N3" s="15" t="s">
+      <c r="N3" s="16" t="s">
         <v>14</v>
       </c>
       <c r="O3" s="16" t="s">
@@ -674,7 +671,7 @@
       <c r="Q3" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="R3" s="16" t="s">
+      <c r="R3" s="17" t="s">
         <v>18</v>
       </c>
       <c r="S3" s="17" t="s">
@@ -695,11 +692,8 @@
       <c r="X3" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="Y3" s="17" t="s">
-        <v>25</v>
-      </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="18"/>
       <c r="B4" s="18"/>
       <c r="C4" s="19"/>
@@ -709,24 +703,23 @@
       <c r="G4" s="20"/>
       <c r="H4" s="20"/>
       <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="20"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="21"/>
       <c r="M4" s="21"/>
-      <c r="N4" s="21"/>
+      <c r="N4" s="22"/>
       <c r="O4" s="22"/>
       <c r="P4" s="22"/>
       <c r="Q4" s="22"/>
-      <c r="R4" s="22"/>
+      <c r="R4" s="23"/>
       <c r="S4" s="23"/>
       <c r="T4" s="23"/>
       <c r="U4" s="23"/>
       <c r="V4" s="23"/>
       <c r="W4" s="23"/>
       <c r="X4" s="23"/>
-      <c r="Y4" s="23"/>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="18"/>
       <c r="B5" s="18"/>
       <c r="C5" s="19"/>
@@ -736,24 +729,23 @@
       <c r="G5" s="20"/>
       <c r="H5" s="20"/>
       <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="20"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="21"/>
       <c r="M5" s="21"/>
-      <c r="N5" s="21"/>
+      <c r="N5" s="22"/>
       <c r="O5" s="22"/>
       <c r="P5" s="22"/>
       <c r="Q5" s="22"/>
-      <c r="R5" s="22"/>
+      <c r="R5" s="23"/>
       <c r="S5" s="23"/>
       <c r="T5" s="23"/>
       <c r="U5" s="23"/>
       <c r="V5" s="23"/>
       <c r="W5" s="23"/>
       <c r="X5" s="23"/>
-      <c r="Y5" s="23"/>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18"/>
       <c r="B6" s="18"/>
       <c r="C6" s="19"/>
@@ -763,24 +755,23 @@
       <c r="G6" s="20"/>
       <c r="H6" s="20"/>
       <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="20"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="21"/>
       <c r="M6" s="21"/>
-      <c r="N6" s="21"/>
+      <c r="N6" s="22"/>
       <c r="O6" s="22"/>
       <c r="P6" s="22"/>
       <c r="Q6" s="22"/>
-      <c r="R6" s="22"/>
+      <c r="R6" s="23"/>
       <c r="S6" s="23"/>
       <c r="T6" s="23"/>
       <c r="U6" s="23"/>
       <c r="V6" s="23"/>
       <c r="W6" s="23"/>
       <c r="X6" s="23"/>
-      <c r="Y6" s="23"/>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18"/>
       <c r="B7" s="18"/>
       <c r="C7" s="19"/>
@@ -790,22 +781,21 @@
       <c r="G7" s="20"/>
       <c r="H7" s="20"/>
       <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="21"/>
-      <c r="L7" s="20"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="21"/>
       <c r="M7" s="21"/>
-      <c r="N7" s="21"/>
+      <c r="N7" s="22"/>
       <c r="O7" s="22"/>
       <c r="P7" s="22"/>
       <c r="Q7" s="22"/>
-      <c r="R7" s="22"/>
+      <c r="R7" s="23"/>
       <c r="S7" s="23"/>
       <c r="T7" s="23"/>
       <c r="U7" s="23"/>
       <c r="V7" s="23"/>
       <c r="W7" s="23"/>
       <c r="X7" s="23"/>
-      <c r="Y7" s="23"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
